--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115701210</v>
+        <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>96238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>2383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Prästgrundet, Nordmaling, Ång</t>
+          <t>Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723134</v>
+        <v>723194</v>
       </c>
       <c r="R2" t="n">
-        <v>7056386</v>
+        <v>7056280</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ropande</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,81 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115701210</t>
+          <t>https://artportalen.se/Sighting/137295945</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109778619</v>
+        <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>58238</v>
+        <v>96238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>2383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Prästgrundet, Nordmaling, Ång</t>
+          <t>Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723253</v>
+        <v>723483</v>
       </c>
       <c r="R3" t="n">
-        <v>7056252</v>
+        <v>7056180</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,16 +887,1846 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Urban Lundström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Urban Lundström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296270</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137296271</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96238</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Plagiomnium medium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>723475</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7056191</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296271</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137296274</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96238</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Plagiomnium medium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>723417</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7056153</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296274</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137296284</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plagiomnium medium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723210</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7056132</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296284</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137296276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98127</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2617</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flikbålmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Riccardia multifida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>723358</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7056125</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296276</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137295970</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96616</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>722969</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7056445</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137295970</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137296268</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96631</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>723491</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7056178</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296268</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137295952</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>723061</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7056398</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>På klen murken gråalslåga.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137295952</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137295953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>723061</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7056386</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137295953</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137295969</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>722976</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7056400</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>På murken gråalslåga</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137295969</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137295971</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>722972</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7056442</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Murken gråalslåga</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137295971</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137296213</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>723464</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7056070</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296213</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137296269</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>723491</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7056118</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296269</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137296277</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96739</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>723267</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7056104</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137296277</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115701210</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Prästgrundet, Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>723134</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056386</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ropande</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115701210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137295972</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58473</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>722965</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7056456</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137295972</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>109778619</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Prästgrundet, Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>723253</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056252</v>
+      </c>
+      <c r="S19" t="n">
+        <v>18</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Urban Lundström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Urban Lundström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109778619</t>
         </is>
@@ -929,6 +2736,22 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96238</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96238</v>
+        <v>96239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96238</v>
+        <v>96239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96238</v>
+        <v>96239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96238</v>
+        <v>96239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98127</v>
+        <v>98128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
+        <v>96244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
+        <v>96244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96239</v>
+        <v>96244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96239</v>
+        <v>96244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96239</v>
+        <v>96244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98128</v>
+        <v>98133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137295972</v>
       </c>
       <c r="B18" t="n">
-        <v>58473</v>
+        <v>58474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96244</v>
+        <v>96246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96244</v>
+        <v>96246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96244</v>
+        <v>96246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96244</v>
+        <v>96246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96244</v>
+        <v>96246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96246</v>
+        <v>96252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96246</v>
+        <v>96252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96246</v>
+        <v>96252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96246</v>
+        <v>96252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96246</v>
+        <v>96252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98135</v>
+        <v>98141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137295972</v>
       </c>
       <c r="B18" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96252</v>
+        <v>96264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
+        <v>96264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96252</v>
+        <v>96264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96252</v>
+        <v>96264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96252</v>
+        <v>96264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98141</v>
+        <v>98153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96264</v>
+        <v>96265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98153</v>
+        <v>98154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96265</v>
+        <v>96268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96265</v>
+        <v>96268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96265</v>
+        <v>96268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96265</v>
+        <v>96268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96265</v>
+        <v>96268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137295945</v>
       </c>
       <c r="B2" t="n">
-        <v>96268</v>
+        <v>96272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137296270</v>
       </c>
       <c r="B3" t="n">
-        <v>96268</v>
+        <v>96272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137296271</v>
       </c>
       <c r="B4" t="n">
-        <v>96268</v>
+        <v>96272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137296274</v>
       </c>
       <c r="B5" t="n">
-        <v>96268</v>
+        <v>96272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137296284</v>
       </c>
       <c r="B6" t="n">
-        <v>96268</v>
+        <v>96272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137296276</v>
       </c>
       <c r="B7" t="n">
-        <v>98157</v>
+        <v>98161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137295970</v>
       </c>
       <c r="B8" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137296268</v>
       </c>
       <c r="B9" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137295952</v>
       </c>
       <c r="B10" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137295953</v>
       </c>
       <c r="B11" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137295969</v>
       </c>
       <c r="B12" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137295971</v>
       </c>
       <c r="B13" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137296213</v>
       </c>
       <c r="B14" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137296269</v>
       </c>
       <c r="B15" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137296277</v>
       </c>
       <c r="B16" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137295972</v>
       </c>
       <c r="B18" t="n">
-        <v>58476</v>
+        <v>58479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
